--- a/Stats Sheet/Round Gaps/Seasons.xlsx
+++ b/Stats Sheet/Round Gaps/Seasons.xlsx
@@ -37,7 +37,7 @@
     <x:t>x</x:t>
   </x:si>
   <x:si>
-    <x:t>67</x:t>
+    <x:t>116</x:t>
   </x:si>
   <x:si>
     <x:t>ACommonKiwi</x:t>
@@ -46,7 +46,7 @@
     <x:t>CaesarOctavius</x:t>
   </x:si>
   <x:si>
-    <x:t>126</x:t>
+    <x:t>175</x:t>
   </x:si>
   <x:si>
     <x:t>FluffyAri</x:t>
@@ -530,7 +530,7 @@
         <x:v>46018</x:v>
       </x:c>
       <x:c r="I1" s="1">
-        <x:v>46018</x:v>
+        <x:v>46067</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9">
@@ -544,7 +544,7 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>0</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
